--- a/docentes/Desc Desc Desc - Estadisticos 20241.xlsx
+++ b/docentes/Desc Desc Desc - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -92,6 +92,60 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>RASCON</t>
+  </si>
+  <si>
+    <t>TRONCO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>VICTOR ALEXIS</t>
+  </si>
+  <si>
+    <t>JONATHAN ISRAEL</t>
+  </si>
+  <si>
+    <t>ANGEL BRYAN</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>IVANNA GUADALUPE</t>
   </si>
 </sst>
 </file>
@@ -791,16 +845,19 @@
         <v>41</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>41</v>
       </c>
-      <c r="E2">
-        <v>41</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -814,16 +871,19 @@
         <v>48</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>48</v>
       </c>
-      <c r="E3">
-        <v>48</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -837,16 +897,19 @@
         <v>36</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>36</v>
       </c>
-      <c r="E4">
-        <v>36</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -860,16 +923,19 @@
         <v>37</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>37</v>
       </c>
-      <c r="E5">
-        <v>37</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -883,16 +949,19 @@
         <v>33</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>33</v>
       </c>
-      <c r="E6">
-        <v>33</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -975,16 +1044,19 @@
         <v>23</v>
       </c>
       <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>23</v>
       </c>
-      <c r="E10">
-        <v>23</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
       <c r="G10">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H10">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -998,16 +1070,19 @@
         <v>19</v>
       </c>
       <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>19</v>
       </c>
-      <c r="E11">
-        <v>19</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
       <c r="G11">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H11">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1063,16 +1138,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>75.61</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1089,16 +1164,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>97.92</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1316,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1346,6 +1421,144 @@
         <v>24</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>24330051920063</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>24330051920337</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>24330051920109</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>24330051920062</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>24330051920314</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>24330051920068</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Desc Desc Desc - Estadisticos 20241.xlsx
+++ b/docentes/Desc Desc Desc - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="50">
   <si>
     <t>Mat</t>
   </si>
@@ -94,12 +94,18 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
     <t>PERALTA</t>
   </si>
   <si>
@@ -112,6 +118,12 @@
     <t>TZITZIHUA</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
     <t>VENTURA</t>
   </si>
   <si>
@@ -128,6 +140,15 @@
   </si>
   <si>
     <t>OSORIO</t>
+  </si>
+  <si>
+    <t>CRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>SANDRA PAOLA</t>
+  </si>
+  <si>
+    <t>ARELI CICLARI</t>
   </si>
   <si>
     <t>URIEL</t>
@@ -975,16 +996,19 @@
         <v>40</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>40</v>
       </c>
-      <c r="E7">
-        <v>40</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -998,16 +1022,19 @@
         <v>34</v>
       </c>
       <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>34</v>
       </c>
-      <c r="E8">
-        <v>34</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1021,16 +1048,19 @@
         <v>33</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>33</v>
       </c>
-      <c r="E9">
-        <v>33</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1268,16 +1298,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1294,16 +1324,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1320,16 +1350,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1391,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1423,16 +1453,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920063</v>
+        <v>24330051920071</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1446,22 +1476,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920337</v>
+        <v>24330051920184</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1469,22 +1499,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920109</v>
+        <v>24330051920217</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1492,16 +1522,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920062</v>
+        <v>24330051920063</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1510,21 +1540,21 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920314</v>
+        <v>24330051920337</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1533,21 +1563,21 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920068</v>
+        <v>24330051920109</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1556,7 +1586,76 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>24330051920062</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>24330051920314</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920068</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
